--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rejoice\data_projects\crucial_sales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECFDB22-9EC8-4897-AC4D-B065293F90F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CAF3EE-8112-430C-B09F-F3C8284896F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="131">
   <si>
     <t>txn_id</t>
   </si>
@@ -378,33 +378,12 @@
     <t>Beauteous Lodge</t>
   </si>
   <si>
-    <t>2026-02-26 058</t>
-  </si>
-  <si>
-    <t>2026-02-26 038</t>
-  </si>
-  <si>
-    <t>2026-02-26 032</t>
-  </si>
-  <si>
-    <t>2026-02-26 011</t>
-  </si>
-  <si>
-    <t>2026-02-26 051</t>
-  </si>
-  <si>
-    <t>2026-02-26 050</t>
-  </si>
-  <si>
     <t>Perpetual</t>
   </si>
   <si>
     <t>Tefund 2</t>
   </si>
   <si>
-    <t>Haqquai</t>
-  </si>
-  <si>
     <t>Aunty Nurse</t>
   </si>
   <si>
@@ -433,6 +412,9 @@
   </si>
   <si>
     <t>lending</t>
+  </si>
+  <si>
+    <t>Hauwal</t>
   </si>
 </sst>
 </file>
@@ -516,9 +498,6 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
@@ -560,6 +539,9 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -664,11 +646,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{51C19E20-08D9-4C70-9C1C-AC7A1F3005ED}" name="Table1" displayName="Table1" ref="A1:G96" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
-  <autoFilter ref="A1:G96" xr:uid="{51C19E20-08D9-4C70-9C1C-AC7A1F3005ED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{51C19E20-08D9-4C70-9C1C-AC7A1F3005ED}" name="Table1" displayName="Table1" ref="A1:G95" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:G95" xr:uid="{51C19E20-08D9-4C70-9C1C-AC7A1F3005ED}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{50D6E4F3-46C0-4B85-BEC3-0AB87851FE18}" name="txn_id"/>
-    <tableColumn id="2" xr3:uid="{9D05FCA0-BBCC-4525-973B-E0C92DE0B309}" name="date" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{9D05FCA0-BBCC-4525-973B-E0C92DE0B309}" name="date" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{A783113F-BD72-4B22-846C-CD0ADD549185}" name="category"/>
     <tableColumn id="4" xr3:uid="{86835934-0AAB-4185-8861-FED43F29D80D}" name="amount"/>
     <tableColumn id="5" xr3:uid="{584CA527-539D-47B0-9BFA-F06ED6D0D60A}" name="type"/>
@@ -680,7 +662,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C48A20D5-10F0-40E2-AA62-76ADB5B21360}" name="Table2" displayName="Table2" ref="A1:C56" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C48A20D5-10F0-40E2-AA62-76ADB5B21360}" name="Table2" displayName="Table2" ref="A1:C56" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:C56" xr:uid="{C48A20D5-10F0-40E2-AA62-76ADB5B21360}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{BC911A03-0D36-442F-B5B8-772248F2FBCD}" name="item_id"/>
@@ -692,13 +674,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A59A43ED-7BFE-4904-97B1-06438E7B5F0D}" name="Table3" displayName="Table3" ref="A1:F23" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A59A43ED-7BFE-4904-97B1-06438E7B5F0D}" name="Table3" displayName="Table3" ref="A1:F23" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:F23" xr:uid="{A59A43ED-7BFE-4904-97B1-06438E7B5F0D}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{F616C20A-0E79-4B44-A5CB-0812AA662350}" name="person_id"/>
     <tableColumn id="2" xr3:uid="{E51FD019-2B40-44BF-9560-CA4146C3A75C}" name="name"/>
     <tableColumn id="3" xr3:uid="{326FC461-BE0E-4DE0-91E7-379B5FE2F377}" name="addr"/>
-    <tableColumn id="4" xr3:uid="{DBFF2A3F-65CD-44E4-A6F3-A47FBB1869BE}" name="cus_date" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{DBFF2A3F-65CD-44E4-A6F3-A47FBB1869BE}" name="cus_date" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{68661BA7-9184-4E2C-A2D8-E683A7AD6F82}" name="phone"/>
     <tableColumn id="6" xr3:uid="{83E7BFDD-236B-4410-8316-6985819BFF0C}" name="role"/>
   </tableColumns>
@@ -993,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -2830,13 +2812,10 @@
       <c r="F88">
         <v>17</v>
       </c>
-      <c r="G88" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" s="1">
         <v>46083</v>
@@ -2851,15 +2830,15 @@
         <v>11</v>
       </c>
       <c r="F89">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="1">
         <v>46083</v>
@@ -2868,21 +2847,21 @@
         <v>8</v>
       </c>
       <c r="D90">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="F90">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" s="1">
         <v>46083</v>
@@ -2900,12 +2879,12 @@
         <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" s="1">
         <v>46083</v>
@@ -2914,21 +2893,21 @@
         <v>8</v>
       </c>
       <c r="D92">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="E92" t="s">
         <v>11</v>
       </c>
       <c r="F92">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G92" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" s="1">
         <v>46083</v>
@@ -2946,12 +2925,12 @@
         <v>20</v>
       </c>
       <c r="G93" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" s="1">
         <v>46083</v>
@@ -2966,52 +2945,29 @@
         <v>11</v>
       </c>
       <c r="F94">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G94" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>129</v>
       </c>
       <c r="D95">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="E95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F95">
-        <v>21</v>
-      </c>
-      <c r="G95" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" s="1">
-        <v>46082</v>
-      </c>
-      <c r="C96" t="s">
-        <v>136</v>
-      </c>
-      <c r="D96">
-        <v>12000</v>
-      </c>
-      <c r="E96" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96">
         <v>0</v>
       </c>
     </row>
@@ -3714,7 +3670,7 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D3" s="1">
         <v>46081</v>
@@ -3734,7 +3690,7 @@
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D4" s="1">
         <v>46081</v>
@@ -3754,7 +3710,7 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D5" s="1">
         <v>46081</v>
@@ -3774,7 +3730,7 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D6" s="1">
         <v>46081</v>
@@ -4031,16 +3987,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D19" s="1">
         <v>46083</v>
       </c>
       <c r="E19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F19" t="s">
         <v>103</v>
@@ -4051,16 +4007,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D20" s="1">
         <v>46083</v>
       </c>
       <c r="E20" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F20" t="s">
         <v>103</v>
@@ -4071,16 +4027,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D21" s="1">
         <v>46083</v>
       </c>
       <c r="E21" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F21" t="s">
         <v>103</v>
@@ -4091,16 +4047,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D22" s="1">
         <v>46083</v>
       </c>
       <c r="E22" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F22" t="s">
         <v>103</v>
@@ -4111,16 +4067,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D23" s="1">
         <v>46083</v>
       </c>
       <c r="E23" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F23" t="s">
         <v>103</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,38 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rejoice\data_projects\crucial_sales\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5386371-A92C-4182-ACEC-7A485ECF8B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
     <sheet name="Persons" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="89">
   <si>
     <t>txn_id</t>
   </si>
@@ -64,9 +47,24 @@
     <t>sales</t>
   </si>
   <si>
+    <t>loan</t>
+  </si>
+  <si>
     <t>purchases</t>
   </si>
   <si>
+    <t>salaries</t>
+  </si>
+  <si>
+    <t>capital</t>
+  </si>
+  <si>
+    <t>bank charges</t>
+  </si>
+  <si>
+    <t>refund</t>
+  </si>
+  <si>
     <t>debit</t>
   </si>
   <si>
@@ -175,6 +173,21 @@
     <t>Destiny</t>
   </si>
   <si>
+    <t>Blessing</t>
+  </si>
+  <si>
+    <t>Loveth</t>
+  </si>
+  <si>
+    <t>Abigail</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
     <t>Beauteous Lodge</t>
   </si>
   <si>
@@ -238,6 +251,9 @@
     <t>07015515307</t>
   </si>
   <si>
+    <t>09016978742</t>
+  </si>
+  <si>
     <t>08167491188</t>
   </si>
   <si>
@@ -247,32 +263,35 @@
     <t>0806547428</t>
   </si>
   <si>
+    <t>09128574227</t>
+  </si>
+  <si>
+    <t>07043452364</t>
+  </si>
+  <si>
+    <t>09037695295</t>
+  </si>
+  <si>
+    <t>08121254628</t>
+  </si>
+  <si>
+    <t>09094498764</t>
+  </si>
+  <si>
     <t>CEO</t>
   </si>
   <si>
     <t>customer</t>
-  </si>
-  <si>
-    <t>loan</t>
-  </si>
-  <si>
-    <t>09016978742</t>
-  </si>
-  <si>
-    <t>salaries</t>
-  </si>
-  <si>
-    <t>capital</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,7 +331,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -322,165 +343,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}" name="Table1" displayName="Table1" ref="A1:H44" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
-  <autoFilter ref="A1:H44" xr:uid="{5687A707-2FB8-42A8-86F4-54A8763C6A1B}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C0FD0D9F-9597-4679-9F73-63FF804A0881}" name="txn_id"/>
-    <tableColumn id="2" xr3:uid="{FF9D134A-CB66-4B80-9E10-D3C9D3780E4A}" name="date" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B78FB8F2-ACCF-4D34-91A8-01D998CEA763}" name="category"/>
-    <tableColumn id="4" xr3:uid="{70517F54-68D9-4A92-90B1-9BD2DF311283}" name="amount"/>
-    <tableColumn id="5" xr3:uid="{27CFA9CD-28BA-4548-B7C9-F1BC6E21921A}" name="type"/>
-    <tableColumn id="6" xr3:uid="{446402EC-6723-4874-AF3A-1A07CF59F634}" name="person_id"/>
-    <tableColumn id="7" xr3:uid="{92A8F572-CE54-4030-A68C-1C68A5D99C3B}" name="item_category"/>
-    <tableColumn id="8" xr3:uid="{4D36E210-9AFD-4F1B-B365-31DBD356C0F2}" name="qty"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{95725E76-239B-411F-9E09-B19577DC4C41}" name="Table2" displayName="Table2" ref="A1:F23" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
-  <autoFilter ref="A1:F23" xr:uid="{95725E76-239B-411F-9E09-B19577DC4C41}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0FBCC40A-F2FC-48B1-AFDC-AF256BA67F47}" name="person_id"/>
-    <tableColumn id="2" xr3:uid="{B8A1BF6E-529F-4B1B-83B9-36B3C0D9E941}" name="name"/>
-    <tableColumn id="3" xr3:uid="{4EE53A3A-B714-47ED-B4BC-B9F59726A744}" name="addr"/>
-    <tableColumn id="4" xr3:uid="{0153F1B2-390B-4E9D-9217-7EDE86D2FDEE}" name="cus_date" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{51636820-D4A1-44D8-A773-FE4F3F4ABA6B}" name="phone" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{A49D98AD-4193-4BEB-B898-697D3B181E7F}" name="role"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -518,7 +399,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -552,7 +433,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -587,10 +467,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -763,53 +642,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H59"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>46079</v>
       </c>
       <c r="C2" t="s">
@@ -819,14 +686,14 @@
         <v>1200</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>46081</v>
       </c>
       <c r="C3" t="s">
@@ -836,14 +703,14 @@
         <v>500</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>46081</v>
       </c>
       <c r="C4" t="s">
@@ -853,23 +720,23 @@
         <v>4000</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>46081</v>
       </c>
       <c r="C5" t="s">
@@ -879,23 +746,23 @@
         <v>2500</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>46081</v>
       </c>
       <c r="C6" t="s">
@@ -905,23 +772,23 @@
         <v>2000</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>46081</v>
       </c>
       <c r="C7" t="s">
@@ -931,23 +798,23 @@
         <v>2000</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>46081</v>
       </c>
       <c r="C8" t="s">
@@ -957,23 +824,23 @@
         <v>2000</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>46081</v>
       </c>
       <c r="C9" t="s">
@@ -983,23 +850,23 @@
         <v>3000</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9">
         <v>6</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>46081</v>
       </c>
       <c r="C10" t="s">
@@ -1009,23 +876,23 @@
         <v>2000</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F10">
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>46081</v>
       </c>
       <c r="C11" t="s">
@@ -1035,23 +902,23 @@
         <v>2000</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>46081</v>
       </c>
       <c r="C12" t="s">
@@ -1061,23 +928,23 @@
         <v>4000</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>46081</v>
       </c>
       <c r="C13" t="s">
@@ -1087,23 +954,23 @@
         <v>3800</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F13">
         <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>46081</v>
       </c>
       <c r="C14" t="s">
@@ -1113,23 +980,23 @@
         <v>8000</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F14">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>46081</v>
       </c>
       <c r="C15" t="s">
@@ -1139,23 +1006,23 @@
         <v>10500</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F15">
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2">
         <v>46081</v>
       </c>
       <c r="C16" t="s">
@@ -1165,23 +1032,23 @@
         <v>6000</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F16">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2">
         <v>46081</v>
       </c>
       <c r="C17" t="s">
@@ -1191,23 +1058,23 @@
         <v>2000</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <v>46081</v>
       </c>
       <c r="C18" t="s">
@@ -1217,23 +1084,23 @@
         <v>2000</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F18">
         <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>46081</v>
       </c>
       <c r="C19" t="s">
@@ -1243,23 +1110,23 @@
         <v>2000</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F19">
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <v>46081</v>
       </c>
       <c r="C20" t="s">
@@ -1269,23 +1136,23 @@
         <v>11000</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F20">
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>46081</v>
       </c>
       <c r="C21" t="s">
@@ -1295,23 +1162,23 @@
         <v>7000</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F21">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="2">
         <v>46081</v>
       </c>
       <c r="C22" t="s">
@@ -1321,23 +1188,23 @@
         <v>4000</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F22">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="2">
         <v>46081</v>
       </c>
       <c r="C23" t="s">
@@ -1347,23 +1214,23 @@
         <v>10000</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F23">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="2">
         <v>46081</v>
       </c>
       <c r="C24" t="s">
@@ -1373,23 +1240,23 @@
         <v>2000</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F24">
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="2">
         <v>46081</v>
       </c>
       <c r="C25" t="s">
@@ -1399,23 +1266,23 @@
         <v>2000</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F25">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="2">
         <v>46081</v>
       </c>
       <c r="C26" t="s">
@@ -1425,23 +1292,23 @@
         <v>2000</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F26">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="2">
         <v>46083</v>
       </c>
       <c r="C27" t="s">
@@ -1451,23 +1318,23 @@
         <v>2000</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F27">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="2">
         <v>46083</v>
       </c>
       <c r="C28" t="s">
@@ -1477,23 +1344,23 @@
         <v>2000</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F28">
         <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="2">
         <v>46083</v>
       </c>
       <c r="C29" t="s">
@@ -1503,23 +1370,23 @@
         <v>3000</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F29">
         <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="2">
         <v>46083</v>
       </c>
       <c r="C30" t="s">
@@ -1529,23 +1396,23 @@
         <v>3000</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F30">
         <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="2">
         <v>46083</v>
       </c>
       <c r="C31" t="s">
@@ -1555,23 +1422,23 @@
         <v>2000</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F31">
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="2">
         <v>46083</v>
       </c>
       <c r="C32" t="s">
@@ -1581,765 +1448,1192 @@
         <v>2000</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F32">
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="2">
         <v>46082</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>12000</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="2">
         <v>46079</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34">
         <v>6000</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H34">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="2">
         <v>46079</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35">
         <v>5000</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H35">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="2">
         <v>46079</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D36">
         <v>8000</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="2">
         <v>46079</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37">
         <v>11200</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H37">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="2">
         <v>46079</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38">
         <v>25000</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H38">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="2">
         <v>46079</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39">
         <v>8100</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H39">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="2">
         <v>46079</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40">
         <v>6000</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H40">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="2">
         <v>46079</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41">
         <v>8000</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H41">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="2">
         <v>46081</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D42">
         <v>5000</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="2">
         <v>46084</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="D43">
         <v>5000</v>
       </c>
       <c r="E43" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="2">
         <v>46078</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="D44">
-        <v>78500</v>
+        <v>110550</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
     </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45">
+        <v>42000</v>
+      </c>
+      <c r="E45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46">
+        <v>11000</v>
+      </c>
+      <c r="E46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
+        <v>66000</v>
+      </c>
+      <c r="E47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48">
+        <v>4000</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48">
+        <v>22</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>4000</v>
+      </c>
+      <c r="E49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50">
+        <v>2000</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50">
+        <v>23</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51">
+        <v>2000</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51">
+        <v>24</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52">
+        <v>2000</v>
+      </c>
+      <c r="E52" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>6000</v>
+      </c>
+      <c r="E53" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53">
+        <v>25</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54">
+        <v>2000</v>
+      </c>
+      <c r="E54" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55">
+        <v>2000</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55">
+        <v>26</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>1850</v>
+      </c>
+      <c r="E56" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57">
+        <v>400</v>
+      </c>
+      <c r="E57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58">
+        <v>6600</v>
+      </c>
+      <c r="E58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59">
+        <v>5000</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E4" t="s">
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" t="s">
+        <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E8" t="s">
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E11" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="D11" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
       <c r="F11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="1">
-        <v>46081</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
       <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="1">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2">
         <v>46083</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>67</v>
+      <c r="E19" t="s">
+        <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="1">
+        <v>60</v>
+      </c>
+      <c r="D20" s="2">
         <v>46083</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>74</v>
+      <c r="E20" t="s">
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="1">
+        <v>60</v>
+      </c>
+      <c r="D21" s="2">
         <v>46083</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>68</v>
+      <c r="E21" t="s">
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="1">
+        <v>60</v>
+      </c>
+      <c r="D22" s="2">
         <v>46083</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>69</v>
+      <c r="E22" t="s">
+        <v>80</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="1">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2">
         <v>46083</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>70</v>
+      <c r="E23" t="s">
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="E3:E19 E21:E24" numberStoredAsText="1"/>
-  </ignoredErrors>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="119">
   <si>
     <t>txn_id</t>
   </si>
@@ -188,6 +188,45 @@
     <t>Chelsea</t>
   </si>
   <si>
+    <t>Jessica</t>
+  </si>
+  <si>
+    <t>Samantha</t>
+  </si>
+  <si>
+    <t>Hannah</t>
+  </si>
+  <si>
+    <t>Fati</t>
+  </si>
+  <si>
+    <t>Kimah</t>
+  </si>
+  <si>
+    <t>Vivian</t>
+  </si>
+  <si>
+    <t>Joy</t>
+  </si>
+  <si>
+    <t>Rachael</t>
+  </si>
+  <si>
+    <t>Zara</t>
+  </si>
+  <si>
+    <t>Chinonye</t>
+  </si>
+  <si>
+    <t>Eunice</t>
+  </si>
+  <si>
+    <t>Hafsat</t>
+  </si>
+  <si>
+    <t>Zohot</t>
+  </si>
+  <si>
     <t>Beauteous Lodge</t>
   </si>
   <si>
@@ -200,6 +239,9 @@
     <t>Tefund 2</t>
   </si>
   <si>
+    <t>Hostel B</t>
+  </si>
+  <si>
     <t>09025458334</t>
   </si>
   <si>
@@ -276,6 +318,54 @@
   </si>
   <si>
     <t>09094498764</t>
+  </si>
+  <si>
+    <t>07040222475</t>
+  </si>
+  <si>
+    <t>09030325477</t>
+  </si>
+  <si>
+    <t>08103470120</t>
+  </si>
+  <si>
+    <t>09158837458</t>
+  </si>
+  <si>
+    <t>07078631601</t>
+  </si>
+  <si>
+    <t>0907604801</t>
+  </si>
+  <si>
+    <t>09088433985</t>
+  </si>
+  <si>
+    <t>09155335147</t>
+  </si>
+  <si>
+    <t>09158874301</t>
+  </si>
+  <si>
+    <t>09152361200</t>
+  </si>
+  <si>
+    <t>09038943331</t>
+  </si>
+  <si>
+    <t>09133611294</t>
+  </si>
+  <si>
+    <t>09161108802</t>
+  </si>
+  <si>
+    <t>09027398125</t>
+  </si>
+  <si>
+    <t>09032699772</t>
+  </si>
+  <si>
+    <t>07056713147</t>
   </si>
   <si>
     <t>CEO</t>
@@ -643,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2067,6 +2157,577 @@
       </c>
       <c r="E59" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60">
+        <v>2500</v>
+      </c>
+      <c r="E60" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60">
+        <v>27</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61">
+        <v>2000</v>
+      </c>
+      <c r="E61" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61">
+        <v>28</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62">
+        <v>4000</v>
+      </c>
+      <c r="E62" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62">
+        <v>29</v>
+      </c>
+      <c r="G62" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63">
+        <v>2000</v>
+      </c>
+      <c r="E63" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63">
+        <v>30</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64">
+        <v>2000</v>
+      </c>
+      <c r="E64" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64">
+        <v>31</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65">
+        <v>2000</v>
+      </c>
+      <c r="E65" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65">
+        <v>31</v>
+      </c>
+      <c r="G65" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66">
+        <v>4000</v>
+      </c>
+      <c r="E66" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66">
+        <v>32</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67">
+        <v>4000</v>
+      </c>
+      <c r="E67" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
+        <v>69</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68">
+        <v>4000</v>
+      </c>
+      <c r="E68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68">
+        <v>34</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>70</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69">
+        <v>2000</v>
+      </c>
+      <c r="E69" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69">
+        <v>34</v>
+      </c>
+      <c r="G69" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70">
+        <v>10000</v>
+      </c>
+      <c r="E70" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70">
+        <v>35</v>
+      </c>
+      <c r="G70" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>72</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71">
+        <v>4000</v>
+      </c>
+      <c r="E71" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71">
+        <v>36</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>73</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72">
+        <v>2000</v>
+      </c>
+      <c r="E72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72">
+        <v>37</v>
+      </c>
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>74</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73">
+        <v>12000</v>
+      </c>
+      <c r="E73" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73">
+        <v>37</v>
+      </c>
+      <c r="G73" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>75</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74">
+        <v>5000</v>
+      </c>
+      <c r="E74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74">
+        <v>38</v>
+      </c>
+      <c r="G74" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>76</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75">
+        <v>2000</v>
+      </c>
+      <c r="E75" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75">
+        <v>38</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>77</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>4000</v>
+      </c>
+      <c r="E76" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76">
+        <v>39</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
+        <v>78</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77">
+        <v>4000</v>
+      </c>
+      <c r="E77" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77">
+        <v>40</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>79</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78">
+        <v>2000</v>
+      </c>
+      <c r="E78" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78">
+        <v>41</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>80</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79">
+        <v>10000</v>
+      </c>
+      <c r="E79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79">
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
+        <v>81</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80">
+        <v>20</v>
+      </c>
+      <c r="E80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>82</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C81" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>500</v>
+      </c>
+      <c r="E81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>83</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82">
+        <v>5000</v>
+      </c>
+      <c r="E82" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2107,10 +2768,10 @@
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2121,16 +2782,16 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2">
         <v>46081</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2141,16 +2802,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2">
         <v>46081</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2161,16 +2822,16 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D5" s="2">
         <v>46081</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2181,16 +2842,16 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2">
         <v>46081</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2201,16 +2862,16 @@
         <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2">
         <v>46081</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2221,16 +2882,16 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2">
         <v>46081</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2241,16 +2902,16 @@
         <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2">
         <v>46081</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2261,16 +2922,16 @@
         <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2">
         <v>46081</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2281,16 +2942,16 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2">
         <v>46081</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2301,16 +2962,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2">
         <v>46081</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2321,16 +2982,16 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D13" s="2">
         <v>46081</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2341,16 +3002,16 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D14" s="2">
         <v>46081</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2361,16 +3022,16 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2">
         <v>46081</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2381,16 +3042,16 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D16" s="2">
         <v>46081</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2401,16 +3062,16 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D17" s="2">
         <v>46081</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2421,16 +3082,16 @@
         <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D18" s="2">
         <v>46081</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2441,16 +3102,16 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D19" s="2">
         <v>46083</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2461,16 +3122,16 @@
         <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D20" s="2">
         <v>46083</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2481,16 +3142,16 @@
         <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2">
         <v>46083</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2501,16 +3162,16 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D22" s="2">
         <v>46083</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2521,16 +3182,16 @@
         <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D23" s="2">
         <v>46083</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2541,16 +3202,16 @@
         <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D24" s="2">
         <v>46086</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2561,16 +3222,16 @@
         <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D25" s="2">
         <v>46086</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2581,16 +3242,16 @@
         <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D26" s="2">
         <v>46086</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2601,16 +3262,16 @@
         <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D27" s="2">
         <v>46086</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2621,16 +3282,336 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D28" s="2">
         <v>46086</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E30" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E32" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E36" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E37" t="s">
+        <v>109</v>
+      </c>
+      <c r="F37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E38" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E40" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E41" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E42" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E43" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="119">
   <si>
     <t>txn_id</t>
   </si>
@@ -379,7 +379,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -733,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2158,6 +2158,9 @@
       <c r="E59" t="s">
         <v>17</v>
       </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
@@ -2369,7 +2372,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B68" s="2">
         <v>46088</v>
@@ -2395,7 +2398,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B69" s="2">
         <v>46088</v>
@@ -2421,7 +2424,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B70" s="2">
         <v>46088</v>
@@ -2447,7 +2450,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B71" s="2">
         <v>46088</v>
@@ -2473,7 +2476,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B72" s="2">
         <v>46088</v>
@@ -2499,7 +2502,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2">
         <v>46088</v>
@@ -2525,7 +2528,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2">
         <v>46088</v>
@@ -2534,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="D74">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
@@ -2543,7 +2546,7 @@
         <v>38</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -2551,7 +2554,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2">
         <v>46088</v>
@@ -2560,24 +2563,24 @@
         <v>9</v>
       </c>
       <c r="D75">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
       </c>
       <c r="F75">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G75" t="s">
         <v>18</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2">
         <v>46088</v>
@@ -2592,7 +2595,7 @@
         <v>17</v>
       </c>
       <c r="F76">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G76" t="s">
         <v>18</v>
@@ -2603,7 +2606,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2">
         <v>46088</v>
@@ -2612,24 +2615,24 @@
         <v>9</v>
       </c>
       <c r="D77">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="E77" t="s">
         <v>17</v>
       </c>
       <c r="F77">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G77" t="s">
         <v>18</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2">
         <v>46088</v>
@@ -2638,16 +2641,16 @@
         <v>9</v>
       </c>
       <c r="D78">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="E78" t="s">
         <v>17</v>
       </c>
       <c r="F78">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G78" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2655,79 +2658,102 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2">
         <v>46088</v>
       </c>
       <c r="C79" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D79">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
-      </c>
-      <c r="F79">
-        <v>42</v>
-      </c>
-      <c r="G79" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2">
         <v>46088</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D80">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:8">
       <c r="A81">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2">
         <v>46088</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D81">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:8">
       <c r="A82">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2">
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D82">
-        <v>5000</v>
+        <v>24500</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83">
+        <v>6000</v>
+      </c>
+      <c r="E83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83">
+        <v>16</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
